--- a/RAGU LOS/all_lobs/output/dealer_group_ragu.xlsx
+++ b/RAGU LOS/all_lobs/output/dealer_group_ragu.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed.ali\ragu-los\RAGU LOS\all_lobs\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B64C3A-ED25-4852-B1F2-87BE2BE63A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0115E9B1-A150-496F-B673-2582CB1D611D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23820" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14685" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Tables (Q) first run" sheetId="1" r:id="rId1"/>
     <sheet name="Data Tables (Q)" sheetId="2" r:id="rId2"/>
+    <sheet name="Data Tables (M)" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="39">
   <si>
     <t>Sonic Automotive</t>
   </si>
@@ -124,6 +125,33 @@
   </si>
   <si>
     <t>Expected Gross Loss Impact</t>
+  </si>
+  <si>
+    <t>2026 M01</t>
+  </si>
+  <si>
+    <t>2026 M02</t>
+  </si>
+  <si>
+    <t>2026 M03</t>
+  </si>
+  <si>
+    <t>2026 M04</t>
+  </si>
+  <si>
+    <t>2026 M05</t>
+  </si>
+  <si>
+    <t>2026 M06</t>
+  </si>
+  <si>
+    <t>2026 M07</t>
+  </si>
+  <si>
+    <t>2026 M08</t>
+  </si>
+  <si>
+    <t>2026 M09</t>
   </si>
 </sst>
 </file>
@@ -482,8 +510,8 @@
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
     <col min="2" max="7" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="8.7265625" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.7265625" style="1"/>
+    <col min="8" max="12" width="8.7265625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -5794,4 +5822,2577 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:J87"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>141.68364950546089</v>
+      </c>
+      <c r="C2">
+        <v>141.9411271917941</v>
+      </c>
+      <c r="D2">
+        <v>142.08652390914409</v>
+      </c>
+      <c r="E2">
+        <v>142.28988221993271</v>
+      </c>
+      <c r="F2">
+        <v>142.25202237619669</v>
+      </c>
+      <c r="G2">
+        <v>142.92395403569219</v>
+      </c>
+      <c r="H2">
+        <v>143.55246708212721</v>
+      </c>
+      <c r="I2">
+        <v>143.7232522284535</v>
+      </c>
+      <c r="J2">
+        <v>143.83842027112439</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>1.851848692584241</v>
+      </c>
+      <c r="C3">
+        <v>1.579095318352614</v>
+      </c>
+      <c r="D3">
+        <v>1.5108340485368219</v>
+      </c>
+      <c r="E3">
+        <v>1.39440138026626</v>
+      </c>
+      <c r="F3">
+        <v>2.3511453490922918</v>
+      </c>
+      <c r="G3">
+        <v>2.540353017608481</v>
+      </c>
+      <c r="H3">
+        <v>1.752390912124667</v>
+      </c>
+      <c r="I3">
+        <v>3.235502880649022</v>
+      </c>
+      <c r="J3">
+        <v>3.47749629456905</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>2.2947148500357071</v>
+      </c>
+      <c r="C4">
+        <v>2.1110685585520881</v>
+      </c>
+      <c r="D4">
+        <v>1.7010409267252971</v>
+      </c>
+      <c r="E4">
+        <v>1.128501970271059</v>
+      </c>
+      <c r="F4">
+        <v>2.0420960019389431</v>
+      </c>
+      <c r="G4">
+        <v>0.41111611916953039</v>
+      </c>
+      <c r="H4">
+        <v>0.49306659893772697</v>
+      </c>
+      <c r="I4">
+        <v>1.186824295096623</v>
+      </c>
+      <c r="J4">
+        <v>2.131011685411532</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>-0.6193257792008936</v>
+      </c>
+      <c r="C5">
+        <v>0.27432811722639228</v>
+      </c>
+      <c r="D5">
+        <v>-1.6734059895097912E-2</v>
+      </c>
+      <c r="E5">
+        <v>-0.72128649824647617</v>
+      </c>
+      <c r="F5">
+        <v>-0.704804553046808</v>
+      </c>
+      <c r="G5">
+        <v>-0.75089660785793799</v>
+      </c>
+      <c r="H5">
+        <v>-0.98113911964877576</v>
+      </c>
+      <c r="I5">
+        <v>-0.48507026176903051</v>
+      </c>
+      <c r="J5">
+        <v>-0.7308360124310983</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>-0.27299151480889788</v>
+      </c>
+      <c r="C6">
+        <v>3.8849650686547672E-2</v>
+      </c>
+      <c r="D6">
+        <v>8.5045639706332055E-2</v>
+      </c>
+      <c r="E6">
+        <v>3.1798309950721297E-2</v>
+      </c>
+      <c r="F6">
+        <v>0.108764432121487</v>
+      </c>
+      <c r="G6">
+        <v>-3.94007301611915E-2</v>
+      </c>
+      <c r="H6">
+        <v>-1.5407396901412349E-3</v>
+      </c>
+      <c r="I6">
+        <v>-0.1241068244076773</v>
+      </c>
+      <c r="J6">
+        <v>-0.24021271327003399</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>144.93789575407109</v>
+      </c>
+      <c r="C7">
+        <v>145.9444688366118</v>
+      </c>
+      <c r="D7">
+        <v>145.36671046421739</v>
+      </c>
+      <c r="E7">
+        <v>144.12329738217429</v>
+      </c>
+      <c r="F7">
+        <v>146.04922360630269</v>
+      </c>
+      <c r="G7">
+        <v>145.08512583445111</v>
+      </c>
+      <c r="H7">
+        <v>144.8152447338507</v>
+      </c>
+      <c r="I7">
+        <v>147.53640231802251</v>
+      </c>
+      <c r="J7">
+        <v>148.47587952540391</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>6103549.040000001</v>
+      </c>
+      <c r="C8">
+        <v>9198553.6099999994</v>
+      </c>
+      <c r="D8">
+        <v>13825775.42</v>
+      </c>
+      <c r="E8">
+        <v>10650858.67</v>
+      </c>
+      <c r="F8">
+        <v>8174048.9500000002</v>
+      </c>
+      <c r="G8">
+        <v>7138752.4500000002</v>
+      </c>
+      <c r="H8">
+        <v>7041486.3000000007</v>
+      </c>
+      <c r="I8">
+        <v>4229879.4800000004</v>
+      </c>
+      <c r="J8">
+        <v>3425760.79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>1.5048220645705199</v>
+      </c>
+      <c r="C9">
+        <v>1.426973010627163</v>
+      </c>
+      <c r="D9">
+        <v>1.451428723246369</v>
+      </c>
+      <c r="E9">
+        <v>1.5142474248560689</v>
+      </c>
+      <c r="F9">
+        <v>1.512715823522629</v>
+      </c>
+      <c r="G9">
+        <v>1.517006779089149</v>
+      </c>
+      <c r="H9">
+        <v>1.538811041816073</v>
+      </c>
+      <c r="I9">
+        <v>1.492588850858801</v>
+      </c>
+      <c r="J9">
+        <v>1.515136242946153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10">
+        <v>0.23889987878298419</v>
+      </c>
+      <c r="C10">
+        <v>0.23444500499019219</v>
+      </c>
+      <c r="D10">
+        <v>0.2337850622899095</v>
+      </c>
+      <c r="E10">
+        <v>0.2345457384292754</v>
+      </c>
+      <c r="F10">
+        <v>0.23344622239826451</v>
+      </c>
+      <c r="G10">
+        <v>0.23556286757373129</v>
+      </c>
+      <c r="H10">
+        <v>0.235022010567002</v>
+      </c>
+      <c r="I10">
+        <v>0.23677295463439541</v>
+      </c>
+      <c r="J10">
+        <v>0.2384316101895719</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>140.35055842885421</v>
+      </c>
+      <c r="C13">
+        <v>139.51164965098181</v>
+      </c>
+      <c r="D13">
+        <v>140.1993480076307</v>
+      </c>
+      <c r="E13">
+        <v>140.8238417414845</v>
+      </c>
+      <c r="F13">
+        <v>141.4779673860703</v>
+      </c>
+      <c r="G13">
+        <v>141.73570121164681</v>
+      </c>
+      <c r="H13">
+        <v>141.3317379017621</v>
+      </c>
+      <c r="I13">
+        <v>141.8822164200308</v>
+      </c>
+      <c r="J13">
+        <v>143.62211865398939</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>2.587821623287311</v>
+      </c>
+      <c r="C14">
+        <v>2.275464925783552</v>
+      </c>
+      <c r="D14">
+        <v>1.230183792856792</v>
+      </c>
+      <c r="E14">
+        <v>2.6855132131962591</v>
+      </c>
+      <c r="F14">
+        <v>0.80161519680524407</v>
+      </c>
+      <c r="G14">
+        <v>2.096177679795971</v>
+      </c>
+      <c r="H14">
+        <v>1.5922945034125751</v>
+      </c>
+      <c r="I14">
+        <v>0.9394193344029701</v>
+      </c>
+      <c r="J14">
+        <v>1.891930636757621</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>0.72384867778909423</v>
+      </c>
+      <c r="C15">
+        <v>0.92505285556388772</v>
+      </c>
+      <c r="D15">
+        <v>0.26916324142118431</v>
+      </c>
+      <c r="E15">
+        <v>0.66377517880165604</v>
+      </c>
+      <c r="F15">
+        <v>-0.52063704277505463</v>
+      </c>
+      <c r="G15">
+        <v>-0.48010735562722562</v>
+      </c>
+      <c r="H15">
+        <v>-0.71109587971306198</v>
+      </c>
+      <c r="I15">
+        <v>-0.78510636176021775</v>
+      </c>
+      <c r="J15">
+        <v>-1.0806974336508559</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>1.6803828242893231</v>
+      </c>
+      <c r="C16">
+        <v>1.5987694797325509</v>
+      </c>
+      <c r="D16">
+        <v>1.7482360728229549</v>
+      </c>
+      <c r="E16">
+        <v>1.6836707562946009</v>
+      </c>
+      <c r="F16">
+        <v>2.6040844310644342</v>
+      </c>
+      <c r="G16">
+        <v>2.2937256524633751</v>
+      </c>
+      <c r="H16">
+        <v>2.0283663812639028</v>
+      </c>
+      <c r="I16">
+        <v>1.359018593308577</v>
+      </c>
+      <c r="J16">
+        <v>2.0496702434408962</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>-1.7551075768833919</v>
+      </c>
+      <c r="C17">
+        <v>-1.7457384651866339</v>
+      </c>
+      <c r="D17">
+        <v>-1.347324955042589</v>
+      </c>
+      <c r="E17">
+        <v>-1.011750566358961</v>
+      </c>
+      <c r="F17">
+        <v>-1.5510507919073431</v>
+      </c>
+      <c r="G17">
+        <v>-1.409747638522008</v>
+      </c>
+      <c r="H17">
+        <v>-1.8761963875297489</v>
+      </c>
+      <c r="I17">
+        <v>-2.0858838665834472</v>
+      </c>
+      <c r="J17">
+        <v>-2.1507374160104988</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>143.58750397733661</v>
+      </c>
+      <c r="C18">
+        <v>142.56519844687509</v>
+      </c>
+      <c r="D18">
+        <v>142.09960615968899</v>
+      </c>
+      <c r="E18">
+        <v>144.84505032341801</v>
+      </c>
+      <c r="F18">
+        <v>142.81197917925761</v>
+      </c>
+      <c r="G18">
+        <v>144.23574954975689</v>
+      </c>
+      <c r="H18">
+        <v>142.36510651919579</v>
+      </c>
+      <c r="I18">
+        <v>141.30966411939869</v>
+      </c>
+      <c r="J18">
+        <v>144.3322846845266</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>2405771.2200000002</v>
+      </c>
+      <c r="C19">
+        <v>4201516.83</v>
+      </c>
+      <c r="D19">
+        <v>6393200.5899999999</v>
+      </c>
+      <c r="E19">
+        <v>4868793.82</v>
+      </c>
+      <c r="F19">
+        <v>4627153.07</v>
+      </c>
+      <c r="G19">
+        <v>3678198.58</v>
+      </c>
+      <c r="H19">
+        <v>3402425.25</v>
+      </c>
+      <c r="I19">
+        <v>2345127.5099999998</v>
+      </c>
+      <c r="J19">
+        <v>2040277.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>1.3195661048203271</v>
+      </c>
+      <c r="C20">
+        <v>1.325356498818999</v>
+      </c>
+      <c r="D20">
+        <v>1.3147903570369539</v>
+      </c>
+      <c r="E20">
+        <v>1.3193338890161781</v>
+      </c>
+      <c r="F20">
+        <v>1.257391034336695</v>
+      </c>
+      <c r="G20">
+        <v>1.2776174205033719</v>
+      </c>
+      <c r="H20">
+        <v>1.2954343797096199</v>
+      </c>
+      <c r="I20">
+        <v>1.3426643627336561</v>
+      </c>
+      <c r="J20">
+        <v>1.2939856535567791</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>0.26007296538404839</v>
+      </c>
+      <c r="C21">
+        <v>0.25993912093123761</v>
+      </c>
+      <c r="D21">
+        <v>0.25424749935775132</v>
+      </c>
+      <c r="E21">
+        <v>0.24945357951941369</v>
+      </c>
+      <c r="F21">
+        <v>0.25715786845581923</v>
+      </c>
+      <c r="G21">
+        <v>0.25513925197888582</v>
+      </c>
+      <c r="H21">
+        <v>0.26180280553613933</v>
+      </c>
+      <c r="I21">
+        <v>0.26479834095119209</v>
+      </c>
+      <c r="J21">
+        <v>0.2657248202287214</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>139.23613817720329</v>
+      </c>
+      <c r="C24">
+        <v>138.22301782140329</v>
+      </c>
+      <c r="D24">
+        <v>139.20502590682139</v>
+      </c>
+      <c r="E24">
+        <v>139.30950445243599</v>
+      </c>
+      <c r="F24">
+        <v>140.27214958607399</v>
+      </c>
+      <c r="G24">
+        <v>141.1901668083068</v>
+      </c>
+      <c r="H24">
+        <v>139.25105678524341</v>
+      </c>
+      <c r="I24">
+        <v>140.54428822106291</v>
+      </c>
+      <c r="J24">
+        <v>144.52636458389679</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25">
+        <v>2.5003354940760398</v>
+      </c>
+      <c r="C25">
+        <v>2.3698814720244168</v>
+      </c>
+      <c r="D25">
+        <v>2.1129892546326232</v>
+      </c>
+      <c r="E25">
+        <v>2.249868726602926</v>
+      </c>
+      <c r="F25">
+        <v>1.790003592440911</v>
+      </c>
+      <c r="G25">
+        <v>1.1187872912527721</v>
+      </c>
+      <c r="H25">
+        <v>2.0255094986145541</v>
+      </c>
+      <c r="I25">
+        <v>3.024956972100028</v>
+      </c>
+      <c r="J25">
+        <v>2.7206146328008458</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26">
+        <v>1.537650756896616</v>
+      </c>
+      <c r="C26">
+        <v>1.8831497424503809</v>
+      </c>
+      <c r="D26">
+        <v>0.54549586048428478</v>
+      </c>
+      <c r="E26">
+        <v>1.466422808264886</v>
+      </c>
+      <c r="F26">
+        <v>-0.69020268752079128</v>
+      </c>
+      <c r="G26">
+        <v>1.120417310263282</v>
+      </c>
+      <c r="H26">
+        <v>-0.24891507076962829</v>
+      </c>
+      <c r="I26">
+        <v>2.2005955646638151</v>
+      </c>
+      <c r="J26">
+        <v>-0.20882875535949991</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27">
+        <v>-1.548346640636389</v>
+      </c>
+      <c r="C27">
+        <v>-1.9031773271419661</v>
+      </c>
+      <c r="D27">
+        <v>-1.7417931786499741</v>
+      </c>
+      <c r="E27">
+        <v>-1.8832628227349311</v>
+      </c>
+      <c r="F27">
+        <v>-2.126758363615401</v>
+      </c>
+      <c r="G27">
+        <v>-2.0270876396348072</v>
+      </c>
+      <c r="H27">
+        <v>-2.7074311644959361</v>
+      </c>
+      <c r="I27">
+        <v>-2.4985980373305292</v>
+      </c>
+      <c r="J27">
+        <v>-5.1900117302217899</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28">
+        <v>-0.89555297180718574</v>
+      </c>
+      <c r="C28">
+        <v>-1.2715488093304741</v>
+      </c>
+      <c r="D28">
+        <v>-0.76863018944717654</v>
+      </c>
+      <c r="E28">
+        <v>-0.76027848697195488</v>
+      </c>
+      <c r="F28">
+        <v>-1.08285409485809</v>
+      </c>
+      <c r="G28">
+        <v>-0.42111850536725809</v>
+      </c>
+      <c r="H28">
+        <v>-0.76528121392364101</v>
+      </c>
+      <c r="I28">
+        <v>-0.95099016879694398</v>
+      </c>
+      <c r="J28">
+        <v>-0.89545965782738146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29">
+        <v>140.83022481573241</v>
+      </c>
+      <c r="C29">
+        <v>139.30132289940559</v>
+      </c>
+      <c r="D29">
+        <v>139.35308765384119</v>
+      </c>
+      <c r="E29">
+        <v>140.38225467759699</v>
+      </c>
+      <c r="F29">
+        <v>138.16233803252069</v>
+      </c>
+      <c r="G29">
+        <v>140.98116526482079</v>
+      </c>
+      <c r="H29">
+        <v>137.5549388346688</v>
+      </c>
+      <c r="I29">
+        <v>142.32025255169921</v>
+      </c>
+      <c r="J29">
+        <v>140.95267907328889</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30">
+        <v>1945140.83</v>
+      </c>
+      <c r="C30">
+        <v>2279887.8599999989</v>
+      </c>
+      <c r="D30">
+        <v>4681236.83</v>
+      </c>
+      <c r="E30">
+        <v>1946856.71</v>
+      </c>
+      <c r="F30">
+        <v>1439501.29</v>
+      </c>
+      <c r="G30">
+        <v>1071436.45</v>
+      </c>
+      <c r="H30">
+        <v>1451582.57</v>
+      </c>
+      <c r="I30">
+        <v>950691.38</v>
+      </c>
+      <c r="J30">
+        <v>515574.86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31">
+        <v>1.5952985371020021</v>
+      </c>
+      <c r="C31">
+        <v>1.632793902012059</v>
+      </c>
+      <c r="D31">
+        <v>1.61552404477232</v>
+      </c>
+      <c r="E31">
+        <v>1.630642890125295</v>
+      </c>
+      <c r="F31">
+        <v>1.657338770029688</v>
+      </c>
+      <c r="G31">
+        <v>1.64630630345844</v>
+      </c>
+      <c r="H31">
+        <v>1.7246724702677041</v>
+      </c>
+      <c r="I31">
+        <v>1.699835647853619</v>
+      </c>
+      <c r="J31">
+        <v>2.0872162983497118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32">
+        <v>0.24779361388295981</v>
+      </c>
+      <c r="C32">
+        <v>0.25316498299043533</v>
+      </c>
+      <c r="D32">
+        <v>0.2459804312778168</v>
+      </c>
+      <c r="E32">
+        <v>0.24586112124245649</v>
+      </c>
+      <c r="F32">
+        <v>0.25046934421225842</v>
+      </c>
+      <c r="G32">
+        <v>0.2410159786481037</v>
+      </c>
+      <c r="H32">
+        <v>0.24593258877033769</v>
+      </c>
+      <c r="I32">
+        <v>0.2485855738399563</v>
+      </c>
+      <c r="J32">
+        <v>0.24779228082610541</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" t="s">
+        <v>34</v>
+      </c>
+      <c r="G34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H34" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34" t="s">
+        <v>37</v>
+      </c>
+      <c r="J34" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35">
+        <v>139.1156346104668</v>
+      </c>
+      <c r="C35">
+        <v>139.696033621417</v>
+      </c>
+      <c r="D35">
+        <v>138.83392789051979</v>
+      </c>
+      <c r="E35">
+        <v>139.51469476246109</v>
+      </c>
+      <c r="F35">
+        <v>139.52831719761571</v>
+      </c>
+      <c r="G35">
+        <v>138.15884062017159</v>
+      </c>
+      <c r="H35">
+        <v>139.73180770172911</v>
+      </c>
+      <c r="I35">
+        <v>141.10630542106429</v>
+      </c>
+      <c r="J35">
+        <v>140.80789414724151</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36">
+        <v>5.5230407673771529</v>
+      </c>
+      <c r="C36">
+        <v>5.2891623330133939</v>
+      </c>
+      <c r="D36">
+        <v>5.2115101378077213</v>
+      </c>
+      <c r="E36">
+        <v>5.0533391490510553</v>
+      </c>
+      <c r="F36">
+        <v>5.2791494940358348</v>
+      </c>
+      <c r="G36">
+        <v>5.557944855433135</v>
+      </c>
+      <c r="H36">
+        <v>4.9056653904493714</v>
+      </c>
+      <c r="I36">
+        <v>5.4477934746900587</v>
+      </c>
+      <c r="J36">
+        <v>5.77272984841116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37">
+        <v>-1.944165270860301</v>
+      </c>
+      <c r="C37">
+        <v>-2.162195969956807</v>
+      </c>
+      <c r="D37">
+        <v>-1.395685566620255</v>
+      </c>
+      <c r="E37">
+        <v>-3.0577722360263131</v>
+      </c>
+      <c r="F37">
+        <v>-1.20632104524721</v>
+      </c>
+      <c r="G37">
+        <v>-1.7853833794578819</v>
+      </c>
+      <c r="H37">
+        <v>-2.7702613726719991</v>
+      </c>
+      <c r="I37">
+        <v>-2.699689397399069</v>
+      </c>
+      <c r="J37">
+        <v>-1.0680877310556891</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38">
+        <v>-2.453949222816302</v>
+      </c>
+      <c r="C38">
+        <v>-2.3698994894435148</v>
+      </c>
+      <c r="D38">
+        <v>-2.6869163445509008</v>
+      </c>
+      <c r="E38">
+        <v>-3.105413213491083</v>
+      </c>
+      <c r="F38">
+        <v>-2.1354994432780532</v>
+      </c>
+      <c r="G38">
+        <v>-3.2985650838494678</v>
+      </c>
+      <c r="H38">
+        <v>-3.410526022104138</v>
+      </c>
+      <c r="I38">
+        <v>-2.7874169885554712</v>
+      </c>
+      <c r="J38">
+        <v>-3.5623398394101771</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39">
+        <v>-0.71481848280700977</v>
+      </c>
+      <c r="C39">
+        <v>-0.54191222489991586</v>
+      </c>
+      <c r="D39">
+        <v>-0.88305937888438057</v>
+      </c>
+      <c r="E39">
+        <v>-0.86135727971157872</v>
+      </c>
+      <c r="F39">
+        <v>-0.77483472095662376</v>
+      </c>
+      <c r="G39">
+        <v>-0.88646064067884667</v>
+      </c>
+      <c r="H39">
+        <v>-1.0170881666765941</v>
+      </c>
+      <c r="I39">
+        <v>-0.78591751921678621</v>
+      </c>
+      <c r="J39">
+        <v>-0.87288261430743819</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40">
+        <v>139.52574240136039</v>
+      </c>
+      <c r="C40">
+        <v>139.9111882701302</v>
+      </c>
+      <c r="D40">
+        <v>139.07977673827199</v>
+      </c>
+      <c r="E40">
+        <v>137.54349118228319</v>
+      </c>
+      <c r="F40">
+        <v>140.69081148216969</v>
+      </c>
+      <c r="G40">
+        <v>137.74637637161851</v>
+      </c>
+      <c r="H40">
+        <v>137.43959753072571</v>
+      </c>
+      <c r="I40">
+        <v>140.28107499058311</v>
+      </c>
+      <c r="J40">
+        <v>141.07731381087939</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41">
+        <v>983120.15</v>
+      </c>
+      <c r="C41">
+        <v>1856673.36</v>
+      </c>
+      <c r="D41">
+        <v>2908901.57</v>
+      </c>
+      <c r="E41">
+        <v>1594968.96</v>
+      </c>
+      <c r="F41">
+        <v>2153662.09</v>
+      </c>
+      <c r="G41">
+        <v>1324145.17</v>
+      </c>
+      <c r="H41">
+        <v>1497653.82</v>
+      </c>
+      <c r="I41">
+        <v>1343708.87</v>
+      </c>
+      <c r="J41">
+        <v>1096505.01</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42">
+        <v>1.6946180360283709</v>
+      </c>
+      <c r="C42">
+        <v>1.684882477889579</v>
+      </c>
+      <c r="D42">
+        <v>1.722200512020033</v>
+      </c>
+      <c r="E42">
+        <v>1.7740721893172211</v>
+      </c>
+      <c r="F42">
+        <v>1.6583133692206631</v>
+      </c>
+      <c r="G42">
+        <v>1.7990816400509899</v>
+      </c>
+      <c r="H42">
+        <v>1.813903911225319</v>
+      </c>
+      <c r="I42">
+        <v>1.734378612258648</v>
+      </c>
+      <c r="J42">
+        <v>1.834396740609195</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43">
+        <v>0.2452116926115287</v>
+      </c>
+      <c r="C43">
+        <v>0.2427416032128559</v>
+      </c>
+      <c r="D43">
+        <v>0.2476151339840626</v>
+      </c>
+      <c r="E43">
+        <v>0.24730510399587971</v>
+      </c>
+      <c r="F43">
+        <v>0.2460690674422375</v>
+      </c>
+      <c r="G43">
+        <v>0.2476637234382692</v>
+      </c>
+      <c r="H43">
+        <v>0.24952983095252279</v>
+      </c>
+      <c r="I43">
+        <v>0.24622739313166839</v>
+      </c>
+      <c r="J43">
+        <v>0.24746975163296339</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" t="s">
+        <v>31</v>
+      </c>
+      <c r="D45" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45" t="s">
+        <v>33</v>
+      </c>
+      <c r="F45" t="s">
+        <v>34</v>
+      </c>
+      <c r="G45" t="s">
+        <v>35</v>
+      </c>
+      <c r="H45" t="s">
+        <v>36</v>
+      </c>
+      <c r="I45" t="s">
+        <v>37</v>
+      </c>
+      <c r="J45" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46">
+        <v>143.193540995554</v>
+      </c>
+      <c r="C46">
+        <v>141.64315747968311</v>
+      </c>
+      <c r="D46">
+        <v>143.4512431391442</v>
+      </c>
+      <c r="E46">
+        <v>142.79619604729251</v>
+      </c>
+      <c r="F46">
+        <v>144.94498237865739</v>
+      </c>
+      <c r="G46">
+        <v>146.2366190469784</v>
+      </c>
+      <c r="H46">
+        <v>144.49935578017781</v>
+      </c>
+      <c r="I46">
+        <v>139.698081088279</v>
+      </c>
+      <c r="J46">
+        <v>144.5784030240147</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47">
+        <v>5.4120176623292204</v>
+      </c>
+      <c r="C47">
+        <v>4.0041776125529216</v>
+      </c>
+      <c r="D47">
+        <v>4.0914417403988352</v>
+      </c>
+      <c r="E47">
+        <v>3.8375591718663311</v>
+      </c>
+      <c r="F47">
+        <v>3.2220908981097982</v>
+      </c>
+      <c r="G47">
+        <v>3.8074263206242449</v>
+      </c>
+      <c r="H47">
+        <v>4.4637780377849481</v>
+      </c>
+      <c r="I47">
+        <v>3.5149740288119351</v>
+      </c>
+      <c r="J47">
+        <v>4.3254164213567208</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48">
+        <v>2.20148417348801</v>
+      </c>
+      <c r="C48">
+        <v>0.34022231480150977</v>
+      </c>
+      <c r="D48">
+        <v>1.5705711050383</v>
+      </c>
+      <c r="E48">
+        <v>-0.45782281975231309</v>
+      </c>
+      <c r="F48">
+        <v>-1.3856453457742099</v>
+      </c>
+      <c r="G48">
+        <v>-0.36972210785698362</v>
+      </c>
+      <c r="H48">
+        <v>-0.27091368911079661</v>
+      </c>
+      <c r="I48">
+        <v>1.526062532130253</v>
+      </c>
+      <c r="J48">
+        <v>0.88859553017436588</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49">
+        <v>0.5458846846749148</v>
+      </c>
+      <c r="C49">
+        <v>1.401815679388952</v>
+      </c>
+      <c r="D49">
+        <v>0.75948031877867073</v>
+      </c>
+      <c r="E49">
+        <v>1.144998708813701</v>
+      </c>
+      <c r="F49">
+        <v>-0.62421088662011426</v>
+      </c>
+      <c r="G49">
+        <v>1.17017228799458</v>
+      </c>
+      <c r="H49">
+        <v>-0.12307890498539981</v>
+      </c>
+      <c r="I49">
+        <v>0.35797776747228971</v>
+      </c>
+      <c r="J49">
+        <v>-1.469097979302278</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>16</v>
+      </c>
+      <c r="B50">
+        <v>0.59367911464028478</v>
+      </c>
+      <c r="C50">
+        <v>0.58568284689565264</v>
+      </c>
+      <c r="D50">
+        <v>1.558584944887542</v>
+      </c>
+      <c r="E50">
+        <v>1.1575216099167149</v>
+      </c>
+      <c r="F50">
+        <v>1.7776388450103759</v>
+      </c>
+      <c r="G50">
+        <v>1.177703184649163</v>
+      </c>
+      <c r="H50">
+        <v>0.46724539824982447</v>
+      </c>
+      <c r="I50">
+        <v>-0.67908110532084309</v>
+      </c>
+      <c r="J50">
+        <v>0.1028367078279324</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51">
+        <v>151.9466066306864</v>
+      </c>
+      <c r="C51">
+        <v>147.9750559333221</v>
+      </c>
+      <c r="D51">
+        <v>151.43132124824751</v>
+      </c>
+      <c r="E51">
+        <v>148.47845271813699</v>
+      </c>
+      <c r="F51">
+        <v>147.9348558893833</v>
+      </c>
+      <c r="G51">
+        <v>152.0221987323894</v>
+      </c>
+      <c r="H51">
+        <v>149.0363866221164</v>
+      </c>
+      <c r="I51">
+        <v>144.41801431137259</v>
+      </c>
+      <c r="J51">
+        <v>148.42615370407151</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52">
+        <v>366111.53</v>
+      </c>
+      <c r="C52">
+        <v>952064.4</v>
+      </c>
+      <c r="D52">
+        <v>1676552.87</v>
+      </c>
+      <c r="E52">
+        <v>1141718.19</v>
+      </c>
+      <c r="F52">
+        <v>493129.28</v>
+      </c>
+      <c r="G52">
+        <v>791573.85</v>
+      </c>
+      <c r="H52">
+        <v>537650.32999999996</v>
+      </c>
+      <c r="I52">
+        <v>301024.27</v>
+      </c>
+      <c r="J52">
+        <v>395804.95</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>19</v>
+      </c>
+      <c r="B53">
+        <v>1.404887837974339</v>
+      </c>
+      <c r="C53">
+        <v>1.33954172943974</v>
+      </c>
+      <c r="D53">
+        <v>1.3879910649150791</v>
+      </c>
+      <c r="E53">
+        <v>1.3585010611230619</v>
+      </c>
+      <c r="F53">
+        <v>1.505270972246439</v>
+      </c>
+      <c r="G53">
+        <v>1.3566189472120069</v>
+      </c>
+      <c r="H53">
+        <v>1.460574465047511</v>
+      </c>
+      <c r="I53">
+        <v>1.4200962998231561</v>
+      </c>
+      <c r="J53">
+        <v>1.587158296868362</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54">
+        <v>0.22651886979085309</v>
+      </c>
+      <c r="C54">
+        <v>0.22663310218720489</v>
+      </c>
+      <c r="D54">
+        <v>0.21273450078732081</v>
+      </c>
+      <c r="E54">
+        <v>0.2184639770011898</v>
+      </c>
+      <c r="F54">
+        <v>0.20960515935699461</v>
+      </c>
+      <c r="G54">
+        <v>0.2181756687907262</v>
+      </c>
+      <c r="H54">
+        <v>0.22832506573928821</v>
+      </c>
+      <c r="I54">
+        <v>0.2447011586474406</v>
+      </c>
+      <c r="J54">
+        <v>0.23353090417388669</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56" t="s">
+        <v>32</v>
+      </c>
+      <c r="E56" t="s">
+        <v>33</v>
+      </c>
+      <c r="F56" t="s">
+        <v>34</v>
+      </c>
+      <c r="G56" t="s">
+        <v>35</v>
+      </c>
+      <c r="H56" t="s">
+        <v>36</v>
+      </c>
+      <c r="I56" t="s">
+        <v>37</v>
+      </c>
+      <c r="J56" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57">
+        <v>145.83838076718351</v>
+      </c>
+      <c r="C57">
+        <v>146.70558872144949</v>
+      </c>
+      <c r="D57">
+        <v>146.2336277293997</v>
+      </c>
+      <c r="E57">
+        <v>143.98739107550529</v>
+      </c>
+      <c r="F57">
+        <v>147.06583532909411</v>
+      </c>
+      <c r="G57">
+        <v>144.9532667703904</v>
+      </c>
+      <c r="H57">
+        <v>145.34690226880451</v>
+      </c>
+      <c r="I57">
+        <v>147.0067645827109</v>
+      </c>
+      <c r="J57">
+        <v>144.995347296792</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>13</v>
+      </c>
+      <c r="B58">
+        <v>6.1139299458529024</v>
+      </c>
+      <c r="C58">
+        <v>5.7725030296189743</v>
+      </c>
+      <c r="D58">
+        <v>6.0686753912475524</v>
+      </c>
+      <c r="E58">
+        <v>6.6608843835492166</v>
+      </c>
+      <c r="F58">
+        <v>6.7031229997654984</v>
+      </c>
+      <c r="G58">
+        <v>6.4494238049911701</v>
+      </c>
+      <c r="H58">
+        <v>6.3131979630390447</v>
+      </c>
+      <c r="I58">
+        <v>6.4044273004936096</v>
+      </c>
+      <c r="J58">
+        <v>6.0583060058735896</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59">
+        <v>2.795164628311634</v>
+      </c>
+      <c r="C59">
+        <v>4.4203351926554953E-2</v>
+      </c>
+      <c r="D59">
+        <v>-1.090980428864968</v>
+      </c>
+      <c r="E59">
+        <v>-1.564649735300528</v>
+      </c>
+      <c r="F59">
+        <v>0.61651606242864965</v>
+      </c>
+      <c r="G59">
+        <v>3.420231471280379</v>
+      </c>
+      <c r="H59">
+        <v>-0.91417698843974504</v>
+      </c>
+      <c r="I59">
+        <v>4.6527433930288238</v>
+      </c>
+      <c r="J59">
+        <v>-4.9441954441526557</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60">
+        <v>-9.9809319171180091E-2</v>
+      </c>
+      <c r="C60">
+        <v>-0.93548253050207941</v>
+      </c>
+      <c r="D60">
+        <v>-0.45835104213653632</v>
+      </c>
+      <c r="E60">
+        <v>-1.7045587127013659</v>
+      </c>
+      <c r="F60">
+        <v>-3.161350660515954</v>
+      </c>
+      <c r="G60">
+        <v>0.23696228303105071</v>
+      </c>
+      <c r="H60">
+        <v>-0.89647729792854047</v>
+      </c>
+      <c r="I60">
+        <v>2.1534161395124749</v>
+      </c>
+      <c r="J60">
+        <v>1.081187211106367</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>16</v>
+      </c>
+      <c r="B61">
+        <v>3.0254940055581701</v>
+      </c>
+      <c r="C61">
+        <v>2.9598810000610092</v>
+      </c>
+      <c r="D61">
+        <v>3.080986100257288</v>
+      </c>
+      <c r="E61">
+        <v>3.553130699184579</v>
+      </c>
+      <c r="F61">
+        <v>3.850000000000001</v>
+      </c>
+      <c r="G61">
+        <v>3.32247834975957</v>
+      </c>
+      <c r="H61">
+        <v>3.5249340547672481</v>
+      </c>
+      <c r="I61">
+        <v>3.7516966422948652</v>
+      </c>
+      <c r="J61">
+        <v>1.674141476788225</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B62">
+        <v>157.67316002773501</v>
+      </c>
+      <c r="C62">
+        <v>154.54669357255401</v>
+      </c>
+      <c r="D62">
+        <v>153.83395774990311</v>
+      </c>
+      <c r="E62">
+        <v>150.9321977102372</v>
+      </c>
+      <c r="F62">
+        <v>155.07412373077219</v>
+      </c>
+      <c r="G62">
+        <v>158.3823626794526</v>
+      </c>
+      <c r="H62">
+        <v>153.3743800002425</v>
+      </c>
+      <c r="I62">
+        <v>163.9690480580407</v>
+      </c>
+      <c r="J62">
+        <v>148.86478654640749</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>18</v>
+      </c>
+      <c r="B63">
+        <v>342116.09</v>
+      </c>
+      <c r="C63">
+        <v>406479.2</v>
+      </c>
+      <c r="D63">
+        <v>671064.22</v>
+      </c>
+      <c r="E63">
+        <v>672932.89</v>
+      </c>
+      <c r="F63">
+        <v>242180</v>
+      </c>
+      <c r="G63">
+        <v>672105.70000000007</v>
+      </c>
+      <c r="H63">
+        <v>450658.05</v>
+      </c>
+      <c r="I63">
+        <v>336570.65</v>
+      </c>
+      <c r="J63">
+        <v>388614.42</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>19</v>
+      </c>
+      <c r="B64">
+        <v>1.458563424847175</v>
+      </c>
+      <c r="C64">
+        <v>1.5344376229664869</v>
+      </c>
+      <c r="D64">
+        <v>1.4901779177390919</v>
+      </c>
+      <c r="E64">
+        <v>1.611591292921337</v>
+      </c>
+      <c r="F64">
+        <v>1.781243197605225</v>
+      </c>
+      <c r="G64">
+        <v>1.4300663652473571</v>
+      </c>
+      <c r="H64">
+        <v>1.5307209767729379</v>
+      </c>
+      <c r="I64">
+        <v>1.286976684495899</v>
+      </c>
+      <c r="J64">
+        <v>1.3632954358693179</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>20</v>
+      </c>
+      <c r="B65">
+        <v>0.1917786570634547</v>
+      </c>
+      <c r="C65">
+        <v>0.19271598571341411</v>
+      </c>
+      <c r="D65">
+        <v>0.1909859128534673</v>
+      </c>
+      <c r="E65">
+        <v>0.18424099001164879</v>
+      </c>
+      <c r="F65">
+        <v>0.18</v>
+      </c>
+      <c r="G65">
+        <v>0.18753602357486329</v>
+      </c>
+      <c r="H65">
+        <v>0.1846437992176107</v>
+      </c>
+      <c r="I65">
+        <v>0.18140433368150191</v>
+      </c>
+      <c r="J65">
+        <v>0.2110836931887396</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>26</v>
+      </c>
+      <c r="B67" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67" t="s">
+        <v>31</v>
+      </c>
+      <c r="D67" t="s">
+        <v>32</v>
+      </c>
+      <c r="E67" t="s">
+        <v>33</v>
+      </c>
+      <c r="F67" t="s">
+        <v>34</v>
+      </c>
+      <c r="G67" t="s">
+        <v>35</v>
+      </c>
+      <c r="H67" t="s">
+        <v>36</v>
+      </c>
+      <c r="I67" t="s">
+        <v>37</v>
+      </c>
+      <c r="J67" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>12</v>
+      </c>
+      <c r="B68">
+        <v>138.7474894652168</v>
+      </c>
+      <c r="C68">
+        <v>142.52121463509249</v>
+      </c>
+      <c r="D68">
+        <v>143.957905289313</v>
+      </c>
+      <c r="E68">
+        <v>141.1557937414176</v>
+      </c>
+      <c r="F68">
+        <v>145.0649530933029</v>
+      </c>
+      <c r="G68">
+        <v>142.45059673815379</v>
+      </c>
+      <c r="H68">
+        <v>141.70170330243229</v>
+      </c>
+      <c r="I68">
+        <v>145.886811345148</v>
+      </c>
+      <c r="J68">
+        <v>144.62339822642321</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69">
+        <v>1.8043660643198789</v>
+      </c>
+      <c r="C69">
+        <v>-0.12764857316466299</v>
+      </c>
+      <c r="D69">
+        <v>0.58660773118873522</v>
+      </c>
+      <c r="E69">
+        <v>1.3653018849849159</v>
+      </c>
+      <c r="F69">
+        <v>-1.1640351708968519</v>
+      </c>
+      <c r="G69">
+        <v>-3.0460063832850319</v>
+      </c>
+      <c r="H69">
+        <v>-0.79749273534429221</v>
+      </c>
+      <c r="I69">
+        <v>-0.18186796295788099</v>
+      </c>
+      <c r="J69">
+        <v>-1.1859554026833341</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>14</v>
+      </c>
+      <c r="B70">
+        <v>7.6353780425412996</v>
+      </c>
+      <c r="C70">
+        <v>3.976019535801214</v>
+      </c>
+      <c r="D70">
+        <v>1.9410984712964201</v>
+      </c>
+      <c r="E70">
+        <v>7.0978921270111142E-2</v>
+      </c>
+      <c r="F70">
+        <v>2.53103025106111</v>
+      </c>
+      <c r="G70">
+        <v>1.3062933704746891</v>
+      </c>
+      <c r="H70">
+        <v>2.106638765062014</v>
+      </c>
+      <c r="I70">
+        <v>2.071981530603153</v>
+      </c>
+      <c r="J70">
+        <v>6.9760866340681391E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71">
+        <v>1.488140108575295</v>
+      </c>
+      <c r="C71">
+        <v>1.8503486303693331</v>
+      </c>
+      <c r="D71">
+        <v>1.9249340930222529</v>
+      </c>
+      <c r="E71">
+        <v>1.0781733854553901</v>
+      </c>
+      <c r="F71">
+        <v>4.1250261909400274</v>
+      </c>
+      <c r="G71">
+        <v>4.1208555791691364</v>
+      </c>
+      <c r="H71">
+        <v>2.866109494518422</v>
+      </c>
+      <c r="I71">
+        <v>3.6870221393000899</v>
+      </c>
+      <c r="J71">
+        <v>2.5457413469509951</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>16</v>
+      </c>
+      <c r="B72">
+        <v>-0.28431914167589062</v>
+      </c>
+      <c r="C72">
+        <v>-0.44698849985000227</v>
+      </c>
+      <c r="D72">
+        <v>-0.1322421176423372</v>
+      </c>
+      <c r="E72">
+        <v>0.45574869274654622</v>
+      </c>
+      <c r="F72">
+        <v>0.62075408770965124</v>
+      </c>
+      <c r="G72">
+        <v>-1.7198823647082639</v>
+      </c>
+      <c r="H72">
+        <v>-0.62325040195471049</v>
+      </c>
+      <c r="I72">
+        <v>0.2328435929854577</v>
+      </c>
+      <c r="J72">
+        <v>0.31627193322674552</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73">
+        <v>149.39105453897739</v>
+      </c>
+      <c r="C73">
+        <v>147.77294572824829</v>
+      </c>
+      <c r="D73">
+        <v>148.27830346717809</v>
+      </c>
+      <c r="E73">
+        <v>144.12599662587459</v>
+      </c>
+      <c r="F73">
+        <v>151.1777284521169</v>
+      </c>
+      <c r="G73">
+        <v>143.11185693980431</v>
+      </c>
+      <c r="H73">
+        <v>145.25370842471369</v>
+      </c>
+      <c r="I73">
+        <v>151.69679064507881</v>
+      </c>
+      <c r="J73">
+        <v>146.36921697025829</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>18</v>
+      </c>
+      <c r="B74">
+        <v>221549.41</v>
+      </c>
+      <c r="C74">
+        <v>230309.17</v>
+      </c>
+      <c r="D74">
+        <v>234842.49</v>
+      </c>
+      <c r="E74">
+        <v>71330.850000000006</v>
+      </c>
+      <c r="F74">
+        <v>151867.44</v>
+      </c>
+      <c r="G74">
+        <v>267195.92</v>
+      </c>
+      <c r="H74">
+        <v>252043.32</v>
+      </c>
+      <c r="I74">
+        <v>237762.61</v>
+      </c>
+      <c r="J74">
+        <v>142452.25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>19</v>
+      </c>
+      <c r="B75">
+        <v>1.333287169787656</v>
+      </c>
+      <c r="C75">
+        <v>1.3076681223967921</v>
+      </c>
+      <c r="D75">
+        <v>1.3025144435820579</v>
+      </c>
+      <c r="E75">
+        <v>1.3635227118593689</v>
+      </c>
+      <c r="F75">
+        <v>1.1668624586402521</v>
+      </c>
+      <c r="G75">
+        <v>1.167092872142526</v>
+      </c>
+      <c r="H75">
+        <v>1.2408066112190499</v>
+      </c>
+      <c r="I75">
+        <v>1.191568309542786</v>
+      </c>
+      <c r="J75">
+        <v>1.2611442852151129</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>20</v>
+      </c>
+      <c r="B76">
+        <v>0.23906170202394131</v>
+      </c>
+      <c r="C76">
+        <v>0.24138554999785719</v>
+      </c>
+      <c r="D76">
+        <v>0.2368891731091762</v>
+      </c>
+      <c r="E76">
+        <v>0.22848930438933501</v>
+      </c>
+      <c r="F76">
+        <v>0.22613208446129071</v>
+      </c>
+      <c r="G76">
+        <v>0.25956974806726091</v>
+      </c>
+      <c r="H76">
+        <v>0.24390357717078159</v>
+      </c>
+      <c r="I76">
+        <v>0.23167366295735059</v>
+      </c>
+      <c r="J76">
+        <v>0.23048182952533219</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>27</v>
+      </c>
+      <c r="B78" t="s">
+        <v>30</v>
+      </c>
+      <c r="C78" t="s">
+        <v>31</v>
+      </c>
+      <c r="D78" t="s">
+        <v>32</v>
+      </c>
+      <c r="E78" t="s">
+        <v>33</v>
+      </c>
+      <c r="F78" t="s">
+        <v>34</v>
+      </c>
+      <c r="G78" t="s">
+        <v>35</v>
+      </c>
+      <c r="H78" t="s">
+        <v>36</v>
+      </c>
+      <c r="I78" t="s">
+        <v>37</v>
+      </c>
+      <c r="J78" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79">
+        <v>141.707418390236</v>
+      </c>
+      <c r="C79">
+        <v>142.69038388891741</v>
+      </c>
+      <c r="D79">
+        <v>142.2556629952233</v>
+      </c>
+      <c r="E79">
+        <v>142.3570553834131</v>
+      </c>
+      <c r="F79">
+        <v>142.54487400187341</v>
+      </c>
+      <c r="G79">
+        <v>143.35749216320229</v>
+      </c>
+      <c r="H79">
+        <v>143.07468350720029</v>
+      </c>
+      <c r="I79">
+        <v>144.3935492986156</v>
+      </c>
+      <c r="J79">
+        <v>145.97987697266021</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>13</v>
+      </c>
+      <c r="B80">
+        <v>1.802066139802633</v>
+      </c>
+      <c r="C80">
+        <v>4.8086778492233861E-2</v>
+      </c>
+      <c r="D80">
+        <v>0.83390561227824378</v>
+      </c>
+      <c r="E80">
+        <v>0.77687154223272614</v>
+      </c>
+      <c r="F80">
+        <v>2.0476279989126449</v>
+      </c>
+      <c r="G80">
+        <v>2.1389778141555378</v>
+      </c>
+      <c r="H80">
+        <v>1.293342241166471</v>
+      </c>
+      <c r="I80">
+        <v>1.2313661779943741</v>
+      </c>
+      <c r="J80">
+        <v>-0.185678900499056</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81">
+        <v>3.360415818193657</v>
+      </c>
+      <c r="C81">
+        <v>2.7972295310569</v>
+      </c>
+      <c r="D81">
+        <v>2.5046796248239231</v>
+      </c>
+      <c r="E81">
+        <v>3.3138932261787688</v>
+      </c>
+      <c r="F81">
+        <v>0.73362165374280852</v>
+      </c>
+      <c r="G81">
+        <v>0.43248795339109752</v>
+      </c>
+      <c r="H81">
+        <v>1.1519154737709381</v>
+      </c>
+      <c r="I81">
+        <v>-0.95424477301555699</v>
+      </c>
+      <c r="J81">
+        <v>2.0520963807119998</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82">
+        <v>-0.36479379424347402</v>
+      </c>
+      <c r="C82">
+        <v>1.0265030550193011</v>
+      </c>
+      <c r="D82">
+        <v>0.30129224674655952</v>
+      </c>
+      <c r="E82">
+        <v>-0.31633653867982819</v>
+      </c>
+      <c r="F82">
+        <v>-0.45493991141611939</v>
+      </c>
+      <c r="G82">
+        <v>-1.4603022570772011</v>
+      </c>
+      <c r="H82">
+        <v>-2.0004287119979178</v>
+      </c>
+      <c r="I82">
+        <v>-1.855390846332738</v>
+      </c>
+      <c r="J82">
+        <v>-2.4092189492821201</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>16</v>
+      </c>
+      <c r="B83">
+        <v>-0.38862098939311329</v>
+      </c>
+      <c r="C83">
+        <v>-0.1030365084072787</v>
+      </c>
+      <c r="D83">
+        <v>-0.14139082055280139</v>
+      </c>
+      <c r="E83">
+        <v>-0.133338514194043</v>
+      </c>
+      <c r="F83">
+        <v>-4.3091414378159387E-2</v>
+      </c>
+      <c r="G83">
+        <v>-0.19081559951516611</v>
+      </c>
+      <c r="H83">
+        <v>-0.2514307888352954</v>
+      </c>
+      <c r="I83">
+        <v>-0.3944393570078264</v>
+      </c>
+      <c r="J83">
+        <v>-0.98066441080136135</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>17</v>
+      </c>
+      <c r="B84">
+        <v>146.11648556459571</v>
+      </c>
+      <c r="C84">
+        <v>146.45916674507859</v>
+      </c>
+      <c r="D84">
+        <v>145.7541496585192</v>
+      </c>
+      <c r="E84">
+        <v>145.99814509895069</v>
+      </c>
+      <c r="F84">
+        <v>144.82809232873461</v>
+      </c>
+      <c r="G84">
+        <v>144.27784007415659</v>
+      </c>
+      <c r="H84">
+        <v>143.26808172130441</v>
+      </c>
+      <c r="I84">
+        <v>142.42084050025389</v>
+      </c>
+      <c r="J84">
+        <v>144.45641109278969</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>18</v>
+      </c>
+      <c r="B85">
+        <v>1419013.11</v>
+      </c>
+      <c r="C85">
+        <v>2099544.0699999998</v>
+      </c>
+      <c r="D85">
+        <v>3078913.51</v>
+      </c>
+      <c r="E85">
+        <v>1969644.41</v>
+      </c>
+      <c r="F85">
+        <v>1921715.2</v>
+      </c>
+      <c r="G85">
+        <v>1124537.77</v>
+      </c>
+      <c r="H85">
+        <v>1742643.12</v>
+      </c>
+      <c r="I85">
+        <v>620800.09</v>
+      </c>
+      <c r="J85">
+        <v>447706.99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>19</v>
+      </c>
+      <c r="B86">
+        <v>1.481797081148895</v>
+      </c>
+      <c r="C86">
+        <v>1.3674310499804041</v>
+      </c>
+      <c r="D86">
+        <v>1.424749067783381</v>
+      </c>
+      <c r="E86">
+        <v>1.4774932410467989</v>
+      </c>
+      <c r="F86">
+        <v>1.4898706845439951</v>
+      </c>
+      <c r="G86">
+        <v>1.5862599394010919</v>
+      </c>
+      <c r="H86">
+        <v>1.6433803024568541</v>
+      </c>
+      <c r="I86">
+        <v>1.6276418724236941</v>
+      </c>
+      <c r="J86">
+        <v>1.6894229249493939</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>20</v>
+      </c>
+      <c r="B87">
+        <v>0.24055172841990161</v>
+      </c>
+      <c r="C87">
+        <v>0.236471950120104</v>
+      </c>
+      <c r="D87">
+        <v>0.23701986886504001</v>
+      </c>
+      <c r="E87">
+        <v>0.23690483591705769</v>
+      </c>
+      <c r="F87">
+        <v>0.23561559163397369</v>
+      </c>
+      <c r="G87">
+        <v>0.2377259371359309</v>
+      </c>
+      <c r="H87">
+        <v>0.23859186841193281</v>
+      </c>
+      <c r="I87">
+        <v>0.24063484795725459</v>
+      </c>
+      <c r="J87">
+        <v>0.24900949158287661</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>